--- a/DRIVE/2. Associados/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
+++ b/DRIVE/2. Associados/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\2. Associados\3. Operações\3.1 Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9CEDFF-3C1E-4B2C-8779-730658E698E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8827085-D3DD-4BCF-952E-4AA49287EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -965,6 +965,36 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{E5119F82-6EFA-4B13-AACA-C77A749ECACB}">
+  <we:reference id="81ae7f57-2760-4043-a9cb-e0d36209e808" version="1.3.0.0" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003696" version="1.3.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_LABS_GENERATIVEAI</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I16"/>
